--- a/public/exports/29189722.xlsx
+++ b/public/exports/29189722.xlsx
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">300477, 300478, 300479</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>314</v>
+        <v>2601</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3014752</t>
+          <t xml:space="preserve">3014776</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F9">
-        <v>720</v>
+        <v>306</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -486,11 +486,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F10">
-        <v>306</v>
+        <v>792</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3014776</t>
+          <t xml:space="preserve">3016185</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>792</v>
+        <v>259</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016185</t>
+          <t xml:space="preserve">3016999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F12">
-        <v>259</v>
+        <v>1259</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016999</t>
+          <t xml:space="preserve">3018950</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F13">
-        <v>1259</v>
+        <v>441</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018950</t>
+          <t xml:space="preserve">3018989</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F14">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018989</t>
+          <t xml:space="preserve">3021345</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F15">
-        <v>420</v>
+        <v>774</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021345</t>
+          <t xml:space="preserve">305008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F16">
-        <v>774</v>
+        <v>1045</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5483861</t>
+          <t xml:space="preserve">305008, 305009</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F17">
-        <v>625</v>
+        <v>5698</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484175</t>
+          <t xml:space="preserve">5483861</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>333</v>
+        <v>625</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484206</t>
+          <t xml:space="preserve">5484175</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>453</v>
+        <v>333</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -986,11 +986,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F20">
-        <v>634</v>
+        <v>453</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484209</t>
+          <t xml:space="preserve">5484206</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F21">
-        <v>939</v>
+        <v>634</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485614</t>
+          <t xml:space="preserve">5484209</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F22">
-        <v>1046</v>
+        <v>939</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5486942</t>
+          <t xml:space="preserve">5485614</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F23">
-        <v>2858</v>
+        <v>1046</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">727892, 1337019</t>
+          <t xml:space="preserve">5486942</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F24">
-        <v>560</v>
+        <v>2858</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">727965, 3013089</t>
+          <t xml:space="preserve">727892, 1337019</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F25">
-        <v>277</v>
+        <v>560</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">727972, 3014752</t>
+          <t xml:space="preserve">727965, 3013089</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F26">
-        <v>670</v>
+        <v>277</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">300477, 300478, 300479</t>
+          <t xml:space="preserve">3020770</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="F36">
-        <v>2601</v>
+        <v>2116</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030440</t>
+          <t xml:space="preserve">200030479</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-16</t>
+          <t xml:space="preserve">2020-04-19</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020770</t>
+          <t xml:space="preserve">8581302</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="F37">
-        <v>2116</v>
+        <v>1651</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030479</t>
+          <t xml:space="preserve">200030561</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-19</t>
+          <t xml:space="preserve">2020-04-21</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8581302</t>
+          <t xml:space="preserve">5483861</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F38">
-        <v>1651</v>
+        <v>1050</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030561</t>
+          <t xml:space="preserve">200032107</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-21</t>
+          <t xml:space="preserve">2020-06-02</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,25 +1931,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5483861</t>
+          <t xml:space="preserve">5485174</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>1050</v>
+        <v>666</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032107</t>
+          <t xml:space="preserve">200033573</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-02</t>
+          <t xml:space="preserve">2020-07-06</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485174</t>
+          <t xml:space="preserve">5484337</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,16 +1990,16 @@
         </is>
       </c>
       <c r="F40">
-        <v>666</v>
+        <v>1120</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033573</t>
+          <t xml:space="preserve">200033798</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-06</t>
+          <t xml:space="preserve">2020-07-09</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484337</t>
+          <t xml:space="preserve">3018950</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="F41">
-        <v>1120</v>
+        <v>260</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033798</t>
+          <t xml:space="preserve">200034774</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-09</t>
+          <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018950</t>
+          <t xml:space="preserve">3016636</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="F42">
-        <v>260</v>
+        <v>518</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034774</t>
+          <t xml:space="preserve">200038891</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-02</t>
+          <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016636</t>
+          <t xml:space="preserve">5485651</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F43">
-        <v>518</v>
+        <v>597</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038891</t>
+          <t xml:space="preserve">200054113</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-11</t>
+          <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9594304</t>
+          <t xml:space="preserve">5484865</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44">
-        <v>2841</v>
+        <v>1986</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041521</t>
+          <t xml:space="preserve">311070695</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-22</t>
+          <t xml:space="preserve">2024-08-28</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485651</t>
+          <t xml:space="preserve">5486942</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F45">
-        <v>597</v>
+        <v>1278</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054113</t>
+          <t xml:space="preserve">311090709</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-24</t>
+          <t xml:space="preserve">2025-01-13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">305008, 305009</t>
+          <t xml:space="preserve">7074135</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>5698</v>
+        <v>426</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311025955</t>
+          <t xml:space="preserve">311187315</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-11-08</t>
+          <t xml:space="preserve">2025-11-02</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484865</t>
+          <t xml:space="preserve">3016999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,26 +2340,26 @@
         </is>
       </c>
       <c r="F47">
-        <v>1986</v>
+        <v>8061</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311070695</t>
+          <t xml:space="preserve">311395070</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-28</t>
+          <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2381,35 +2381,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5486942</t>
+          <t xml:space="preserve">3016999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F48">
-        <v>1278</v>
+        <v>390</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311090709</t>
+          <t xml:space="preserve">311395057</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-13</t>
+          <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2431,35 +2431,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7074135</t>
+          <t xml:space="preserve">3016999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F49">
-        <v>426</v>
+        <v>276</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311187315</t>
+          <t xml:space="preserve">311395070</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-02</t>
+          <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016999</t>
+          <t xml:space="preserve">5485003</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2490,11 +2490,11 @@
         </is>
       </c>
       <c r="F50">
-        <v>8061</v>
+        <v>2193</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395070</t>
+          <t xml:space="preserve">311395074</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016999</t>
+          <t xml:space="preserve">5485003</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,11 +2540,11 @@
         </is>
       </c>
       <c r="F51">
-        <v>390</v>
+        <v>2889</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395057</t>
+          <t xml:space="preserve">311395074</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2581,20 +2581,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016999</t>
+          <t xml:space="preserve">5485003</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F52">
-        <v>276</v>
+        <v>734</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395070</t>
+          <t xml:space="preserve">311395074</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2636,11 +2636,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F53">
-        <v>2193</v>
+        <v>430</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2686,11 +2686,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F54">
-        <v>2889</v>
+        <v>1412</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2736,11 +2736,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F55">
-        <v>734</v>
+        <v>1395</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,25 +2781,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485003</t>
+          <t xml:space="preserve">3011650</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>430</v>
+        <v>2675</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395074</t>
+          <t xml:space="preserve">311407572</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-27</t>
+          <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485003</t>
+          <t xml:space="preserve">3020547</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F57">
-        <v>1412</v>
+        <v>2042</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395074</t>
+          <t xml:space="preserve">311407554</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-27</t>
+          <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485003</t>
+          <t xml:space="preserve">5487205</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F58">
-        <v>1395</v>
+        <v>920</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395074</t>
+          <t xml:space="preserve">311407547</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-27</t>
+          <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,20 +2931,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011650</t>
+          <t xml:space="preserve">5487205</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F59">
-        <v>2675</v>
+        <v>920</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407572</t>
+          <t xml:space="preserve">311407547</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2981,20 +2981,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020547</t>
+          <t xml:space="preserve">5487205</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F60">
-        <v>2042</v>
+        <v>953</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407554</t>
+          <t xml:space="preserve">311407547</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F61">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487205</t>
+          <t xml:space="preserve">3020547</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F62">
-        <v>920</v>
+        <v>437</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407547</t>
+          <t xml:space="preserve">311419854</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-06</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487205</t>
+          <t xml:space="preserve">3011652</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F63">
-        <v>953</v>
+        <v>556</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407547</t>
+          <t xml:space="preserve">311408533</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-06</t>
+          <t xml:space="preserve">2029-11-12</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487205</t>
+          <t xml:space="preserve">5487375</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F64">
-        <v>953</v>
+        <v>1549</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407547</t>
+          <t xml:space="preserve">311412074</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-06</t>
+          <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020547</t>
+          <t xml:space="preserve">5487375</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F65">
-        <v>437</v>
+        <v>749</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419854</t>
+          <t xml:space="preserve">311412071</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011652</t>
+          <t xml:space="preserve">3017687</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>556</v>
+        <v>513</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408533</t>
+          <t xml:space="preserve">311414590</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-12</t>
+          <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487375</t>
+          <t xml:space="preserve">3017687</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F67">
-        <v>1549</v>
+        <v>487</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412074</t>
+          <t xml:space="preserve">311414590</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-03</t>
+          <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487375</t>
+          <t xml:space="preserve">3017687</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F68">
-        <v>749</v>
+        <v>459</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412071</t>
+          <t xml:space="preserve">311414590</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-03</t>
+          <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3436,11 +3436,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F69">
-        <v>513</v>
+        <v>613</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F70">
-        <v>487</v>
+        <v>407</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3017687</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>459</v>
+        <v>986</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414590</t>
+          <t xml:space="preserve">311428334</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-18</t>
+          <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3017687</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F72">
-        <v>613</v>
+        <v>314</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414590</t>
+          <t xml:space="preserve">311428341</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-18</t>
+          <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3017687</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F73">
-        <v>407</v>
+        <v>1281</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414590</t>
+          <t xml:space="preserve">311428334</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-18</t>
+          <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3686,15 +3686,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F74">
-        <v>986</v>
+        <v>254</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428334</t>
+          <t xml:space="preserve">311428341</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">3021483</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F75">
-        <v>1281</v>
+        <v>2410</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428334</t>
+          <t xml:space="preserve">311429648</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-17</t>
+          <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">3021483</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F76">
-        <v>254</v>
+        <v>1088</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428343</t>
+          <t xml:space="preserve">311429648</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-17</t>
+          <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3836,11 +3836,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F77">
-        <v>2410</v>
+        <v>368</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3886,11 +3886,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F78">
-        <v>1088</v>
+        <v>479</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3936,11 +3936,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F79">
-        <v>368</v>
+        <v>556</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3986,20 +3986,20 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F80">
-        <v>479</v>
+        <v>332</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311429648</t>
+          <t xml:space="preserve">311432562</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-24</t>
+          <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021483</t>
+          <t xml:space="preserve">100007616</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F81">
-        <v>556</v>
+        <v>1000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311429648</t>
+          <t xml:space="preserve">311459391</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-24</t>
+          <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,25 +4081,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021483</t>
+          <t xml:space="preserve">5485861</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F82">
-        <v>332</v>
+        <v>1206</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311432562</t>
+          <t xml:space="preserve">311459380</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-14</t>
+          <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100007616</t>
+          <t xml:space="preserve">10109499</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,16 +4140,16 @@
         </is>
       </c>
       <c r="F83">
-        <v>1000</v>
+        <v>826</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459391</t>
+          <t xml:space="preserve">311479299</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-07</t>
+          <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485861</t>
+          <t xml:space="preserve">3018989</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="F84">
-        <v>1206</v>
+        <v>5915</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459380</t>
+          <t xml:space="preserve">311479309</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-07</t>
+          <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">10109499</t>
+          <t xml:space="preserve">8053584</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,11 +4240,11 @@
         </is>
       </c>
       <c r="F85">
-        <v>826</v>
+        <v>1157</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479299</t>
+          <t xml:space="preserve">311479296</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018989</t>
+          <t xml:space="preserve">5487254</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,16 +4290,16 @@
         </is>
       </c>
       <c r="F86">
-        <v>5915</v>
+        <v>594</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479309</t>
+          <t xml:space="preserve">311493575</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-30</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8053584</t>
+          <t xml:space="preserve">3014752</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>1157</v>
+        <v>720</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479296</t>
+          <t xml:space="preserve">311572425</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-30</t>
+          <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487254</t>
+          <t xml:space="preserve">5484485</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,16 +4390,16 @@
         </is>
       </c>
       <c r="F88">
-        <v>594</v>
+        <v>424</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493575</t>
+          <t xml:space="preserve">311572484</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,20 +4431,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484485</t>
+          <t xml:space="preserve">727972, 3014752</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F89">
-        <v>424</v>
+        <v>670</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572484</t>
+          <t xml:space="preserve">311572425</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">9594304</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F90">
-        <v>690</v>
+        <v>2841</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575186</t>
+          <t xml:space="preserve">311572368</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-27</t>
+          <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,20 +4531,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584, 100480677</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F91">
-        <v>549</v>
+        <v>690</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575158</t>
+          <t xml:space="preserve">311575186</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018989</t>
+          <t xml:space="preserve">3013584, 100480677</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F92">
-        <v>5226</v>
+        <v>549</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576469</t>
+          <t xml:space="preserve">311575158</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-03</t>
+          <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5486942</t>
+          <t xml:space="preserve">3018989</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F93">
-        <v>1278</v>
+        <v>5226</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576597</t>
+          <t xml:space="preserve">311576469</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4686,15 +4686,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>1470</v>
+        <v>1278</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576575</t>
+          <t xml:space="preserve">311576597</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4736,11 +4736,11 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F95">
-        <v>2096</v>
+        <v>1470</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3017767</t>
+          <t xml:space="preserve">5486942</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F96">
-        <v>282</v>
+        <v>2096</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586393</t>
+          <t xml:space="preserve">311576575</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">727934, 3020550</t>
+          <t xml:space="preserve">3017767</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,16 +4840,16 @@
         </is>
       </c>
       <c r="F97">
-        <v>1300</v>
+        <v>282</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603945</t>
+          <t xml:space="preserve">311586393</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-30</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021483</t>
+          <t xml:space="preserve">727934, 3020550</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>2506</v>
+        <v>1300</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620632</t>
+          <t xml:space="preserve">311603945</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-05-30</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4936,11 +4936,11 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F99">
-        <v>1548</v>
+        <v>2506</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4986,15 +4986,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F100">
-        <v>1076</v>
+        <v>1548</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620639</t>
+          <t xml:space="preserve">311620632</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5031,25 +5031,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485155</t>
+          <t xml:space="preserve">3021483</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F101">
-        <v>4111</v>
+        <v>1076</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643736</t>
+          <t xml:space="preserve">311620639</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,25 +5081,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011660</t>
+          <t xml:space="preserve">5485155</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>1635</v>
+        <v>4111</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644019</t>
+          <t xml:space="preserve">311643736</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,25 +5131,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">100034625</t>
+          <t xml:space="preserve">3011660</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F103">
-        <v>2759</v>
+        <v>1635</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311785873</t>
+          <t xml:space="preserve">311644019</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-19</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5186,15 +5186,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>2095</v>
+        <v>2759</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311785874</t>
+          <t xml:space="preserve">311785873</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5231,25 +5231,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">100034625</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F105">
-        <v>599</v>
+        <v>2095</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789171</t>
+          <t xml:space="preserve">311785874</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-03</t>
+          <t xml:space="preserve">2034-09-19</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,20 +5281,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3022081</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F106">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789178</t>
+          <t xml:space="preserve">311789171</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5331,20 +5331,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485649</t>
+          <t xml:space="preserve">3022081</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>1034</v>
+        <v>666</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789168</t>
+          <t xml:space="preserve">311789178</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011021</t>
+          <t xml:space="preserve">5485649</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F108">
-        <v>713</v>
+        <v>1034</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797133</t>
+          <t xml:space="preserve">311789168</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,20 +5431,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020021</t>
+          <t xml:space="preserve">3011021</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>398</v>
+        <v>713</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797117</t>
+          <t xml:space="preserve">311797133</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8333766</t>
+          <t xml:space="preserve">3020021</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F110">
-        <v>1668</v>
+        <v>398</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797113</t>
+          <t xml:space="preserve">311797117</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9818651</t>
+          <t xml:space="preserve">8333766</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>453</v>
+        <v>1668</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797391</t>
+          <t xml:space="preserve">311797113</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-14</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484167</t>
+          <t xml:space="preserve">9818651</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>2753</v>
+        <v>453</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829568</t>
+          <t xml:space="preserve">311797391</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-06</t>
+          <t xml:space="preserve">2034-11-14</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5636,11 +5636,11 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F113">
-        <v>396</v>
+        <v>2753</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -5681,20 +5681,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484760</t>
+          <t xml:space="preserve">5484167</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F114">
-        <v>923</v>
+        <v>396</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829489</t>
+          <t xml:space="preserve">311829568</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485614</t>
+          <t xml:space="preserve">5484760</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F115">
-        <v>630</v>
+        <v>923</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841344</t>
+          <t xml:space="preserve">311829489</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-27</t>
+          <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">305008</t>
+          <t xml:space="preserve">5485614</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>1045</v>
+        <v>630</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842900</t>
+          <t xml:space="preserve">311841344</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-04</t>
+          <t xml:space="preserve">2035-06-27</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">

--- a/public/exports/29189722.xlsx
+++ b/public/exports/29189722.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:L122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100106793</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>405</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100106793</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>354</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 102</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">101000311</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>408</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 104B</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">101000311</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">28</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>377</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 104</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">101000311</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>398</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnepromenaden 2A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">1337019</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>369</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Egevangsvej 1A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">300477, 300478, 300479</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>2601</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 98A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">3014776</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>306</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 98A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">3014776</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>792</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Griffensund 15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">3016185</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>259</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 1B</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">3016999</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>1259</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svendborgvej 39A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">3018950</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>441</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">3018989</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>420</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alsvej 11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021345</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>774</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,33 +931,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 15</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">305008</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>1045</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -831,33 +991,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Wørishøffersgade 25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t xml:space="preserve">305008, 305009</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>5698</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -881,33 +1051,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 30</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">5483861</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F18">
+      <c r="H18">
         <v>625</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -931,33 +1111,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stendamsgade 2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484175</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F19">
+      <c r="H19">
         <v>333</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -981,33 +1171,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stendamsgade 11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484206</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F20">
+      <c r="H20">
         <v>453</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1031,33 +1231,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stendamsgade 11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484206</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F21">
+      <c r="H21">
         <v>634</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1081,33 +1291,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stendamsgade 9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484209</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F22">
+      <c r="H22">
         <v>939</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,33 +1351,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Provst Hjortsvej 9E</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485614</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F23">
+      <c r="H23">
         <v>1046</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1181,33 +1411,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Storebæltsvej 13</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t xml:space="preserve">5486942</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F24">
+      <c r="H24">
         <v>2858</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1231,33 +1471,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnepromenaden 6</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">727892, 1337019</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="F25">
+      <c r="H25">
         <v>560</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1281,33 +1531,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langtvedvej 11B</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">727965, 3013089</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F26">
+      <c r="H26">
         <v>277</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1331,33 +1591,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Solholm 8B</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">3019569</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F27">
+      <c r="H27">
         <v>542</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">200023926</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1381,33 +1651,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Falstervej 15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021345</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F28">
+      <c r="H28">
         <v>694</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">200026224</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1431,33 +1711,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skippergade 28</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484021</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F29">
+      <c r="H29">
         <v>416</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">200027009</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-01-20</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1481,33 +1771,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langemosevej 3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021484</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F30">
+      <c r="H30">
         <v>264</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">200027854</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1531,33 +1831,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 98</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487205</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F31">
+      <c r="H31">
         <v>1926</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">200028955</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-03-09</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1581,33 +1891,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Provst Hjortsvej 9A</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485651</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F32">
+      <c r="H32">
         <v>1320</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">200029367</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-03-17</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1631,33 +1951,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vægtergade 9</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484150</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F33">
+      <c r="H33">
         <v>413</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">200030325</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1681,33 +2011,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vægtergade 9</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484150</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F34">
+      <c r="H34">
         <v>345</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">200030324</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1731,33 +2071,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vægtergade 9</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484150</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F35">
+      <c r="H35">
         <v>362</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">200030324</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1781,33 +2131,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Alsvej 10</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">3020770</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F36">
+      <c r="H36">
         <v>2116</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">200030479</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-04-19</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1831,33 +2191,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kløvervej 1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">8581302</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F37">
+      <c r="H37">
         <v>1651</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">200030561</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-04-21</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1881,33 +2251,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Havnegade 28</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">5483861</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="H38">
         <v>1050</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">200032107</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-06-02</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1931,33 +2311,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hyrdegyden 4</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485174</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F39">
+      <c r="H39">
         <v>666</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">200033573</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-07-06</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1981,33 +2371,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kgs. Bastionsvej 2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484337</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F40">
+      <c r="H40">
         <v>1120</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">200033798</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-07-09</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2031,33 +2431,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svendborgvej 39</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">3018950</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F41">
+      <c r="H41">
         <v>260</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">200034774</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2081,33 +2491,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dyrehavevej 43</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">3016636</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F42">
+      <c r="H42">
         <v>518</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">200038891</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2131,33 +2551,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Provst Hjortsvej 9B</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485651</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F43">
+      <c r="H43">
         <v>597</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">200054113</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2181,33 +2611,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørrevoldgade 63</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484865</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F44">
+      <c r="H44">
         <v>1986</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">311070695</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-08-28</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2231,33 +2671,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Storebæltsvej 15</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">5486942</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F45">
+      <c r="H45">
         <v>1278</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">311090709</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-01-13</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2281,33 +2731,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kertemindevej 2A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">7074135</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F46">
+      <c r="H46">
         <v>426</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">311187315</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-11-02</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2331,33 +2791,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">3016999</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F47">
+      <c r="H47">
         <v>8061</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">311395070</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2381,33 +2851,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">3016999</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F48">
+      <c r="H48">
         <v>390</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">311395057</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,33 +2911,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 1D</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">3016999</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F49">
+      <c r="H49">
         <v>276</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">311395070</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2481,33 +2971,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485003</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F50">
+      <c r="H50">
         <v>2193</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">311395074</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2531,33 +3031,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485003</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F51">
+      <c r="H51">
         <v>2889</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">311395074</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2581,33 +3091,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485003</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F52">
+      <c r="H52">
         <v>734</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">311395074</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2631,33 +3151,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485003</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F53">
+      <c r="H53">
         <v>430</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">311395074</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2681,33 +3211,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 2A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485003</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F54">
+      <c r="H54">
         <v>1412</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">311395074</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2731,33 +3271,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svanedamsgade 2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485003</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="H55">
         <v>1395</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">311395074</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2781,33 +3331,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kertemindevej 46</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">3011650</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F56">
+      <c r="H56">
         <v>2675</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">311407572</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2831,33 +3391,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 15</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">3020547</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F57">
+      <c r="H57">
         <v>2042</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">311407554</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2881,33 +3451,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 100B</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487205</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F58">
+      <c r="H58">
         <v>920</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">311407547</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2931,33 +3511,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 100E</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487205</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F59">
+      <c r="H59">
         <v>920</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">311407547</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2981,33 +3571,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 100D</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487205</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F60">
+      <c r="H60">
         <v>953</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">311407547</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3031,33 +3631,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 100A</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487205</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="F61">
+      <c r="H61">
         <v>953</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">311407547</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,33 +3691,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 15C</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">3020547</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F62">
+      <c r="H62">
         <v>437</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">311419854</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3131,33 +3751,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kertemindevej 46</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">3011652</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F63">
+      <c r="H63">
         <v>556</v>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">311408533</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-11-12</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3181,33 +3811,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 96</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487375</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F64">
+      <c r="H64">
         <v>1549</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">311412074</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3231,33 +3871,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skaboeshusevej 96</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487375</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F65">
+      <c r="H65">
         <v>749</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">311412071</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3281,33 +3931,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pårupvej 25B</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017687</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F66">
+      <c r="H66">
         <v>513</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">311414590</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3331,33 +3991,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pårupvej 25B</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017687</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F67">
+      <c r="H67">
         <v>487</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">311414590</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3381,33 +4051,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pårupvej 25B</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017687</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F68">
+      <c r="H68">
         <v>459</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">311414590</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3431,33 +4111,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pårupvej 25B</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017687</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F69">
+      <c r="H69">
         <v>613</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">311414590</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3481,33 +4171,43 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pårupvej 25B</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017687</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F70">
+      <c r="H70">
         <v>407</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">311414590</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3531,33 +4231,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F71">
+      <c r="H71">
         <v>986</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t xml:space="preserve">311428334</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3581,33 +4291,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1A</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
         </is>
       </c>
-      <c r="F72">
+      <c r="H72">
         <v>314</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t xml:space="preserve">311428341</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3631,33 +4351,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F73">
+      <c r="H73">
         <v>1281</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">311428334</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3681,33 +4411,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 1</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F74">
+      <c r="H74">
         <v>254</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311428341</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311428343</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,33 +4471,43 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langemosevej 1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="F75">
+      <c r="H75">
         <v>2410</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">311429648</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3781,33 +4531,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sentvedvej 6</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F76">
+      <c r="H76">
         <v>1088</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">311429648</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3831,33 +4591,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sentvedvej 6</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F77">
+      <c r="H77">
         <v>368</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">311429648</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3881,33 +4651,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sentvedvej 6A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F78">
+      <c r="H78">
         <v>479</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">311429648</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3931,33 +4711,43 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langemosevej 1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="F79">
+      <c r="H79">
         <v>556</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">311429648</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3981,33 +4771,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sentvedvej 4</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="F80">
+      <c r="H80">
         <v>332</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">311432562</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4031,33 +4831,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ravnekærlund 1</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">100007616</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F81">
+      <c r="H81">
         <v>1000</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">311459391</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4081,33 +4891,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tårnvej 13</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485861</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F82">
+      <c r="H82">
         <v>1206</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">311459380</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4131,33 +4951,43 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ådalen 1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">10109499</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F83">
+      <c r="H83">
         <v>826</v>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">311479299</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4181,33 +5011,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">3018989</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F84">
+      <c r="H84">
         <v>5915</v>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">311479309</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4231,33 +5071,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sylleskovvej 10</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">8053584</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F85">
+      <c r="H85">
         <v>1157</v>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">311479296</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4281,33 +5131,43 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Harevænget 30</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">5487254</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F86">
+      <c r="H86">
         <v>594</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">311493575</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4331,33 +5191,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 104C</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
           <t xml:space="preserve">3014752</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F87">
+      <c r="H87">
         <v>720</v>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">311572425</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,33 +5251,43 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vestergade 7A</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484485</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F88">
+      <c r="H88">
         <v>424</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t xml:space="preserve">311572484</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4431,33 +5311,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 100</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t xml:space="preserve">727972, 3014752</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F89">
+      <c r="H89">
         <v>670</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">311572425</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4481,33 +5371,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevænget 4</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t xml:space="preserve">9594304</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F90">
+      <c r="H90">
         <v>2841</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">311572368</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4531,33 +5431,43 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sportsvænget 4</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F91">
+      <c r="H91">
         <v>690</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t xml:space="preserve">311575186</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4581,33 +5491,43 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sportsvænget 4A</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584, 100480677</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F92">
+      <c r="H92">
         <v>549</v>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t xml:space="preserve">311575158</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4631,33 +5551,43 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t xml:space="preserve">3018989</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F93">
+      <c r="H93">
         <v>5226</v>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t xml:space="preserve">311576469</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4681,33 +5611,43 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Storebæltsvej 15</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t xml:space="preserve">5486942</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F94">
+      <c r="H94">
         <v>1278</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t xml:space="preserve">311576597</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4731,33 +5671,43 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Storebæltsvej 15</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t xml:space="preserve">5486942</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F95">
+      <c r="H95">
         <v>1470</v>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t xml:space="preserve">311576575</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4781,33 +5731,43 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Storebæltsvej 15</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
           <t xml:space="preserve">5486942</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="H96">
         <v>2096</v>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">311576575</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4831,33 +5791,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bytoften 25</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017767</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F97">
+      <c r="H97">
         <v>282</v>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t xml:space="preserve">311586393</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4881,33 +5851,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 15B</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t xml:space="preserve">727934, 3020550</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F98">
+      <c r="H98">
         <v>1300</v>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t xml:space="preserve">311603945</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-05-30</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4931,33 +5911,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langemosevej 5</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="F99">
+      <c r="H99">
         <v>2506</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t xml:space="preserve">311620632</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4981,33 +5971,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langemosevej 5</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="F100">
+      <c r="H100">
         <v>1548</v>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">311620632</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,33 +6031,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Langemosevej 5</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t xml:space="preserve">3021483</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="F101">
+      <c r="H101">
         <v>1076</v>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">311620639</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5081,33 +6091,43 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Halvej 1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485155</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F102">
+      <c r="H102">
         <v>4111</v>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">311643736</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5131,33 +6151,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kertemindevej 50</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t xml:space="preserve">3011660</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F103">
+      <c r="H103">
         <v>1635</v>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311644019</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311644024</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5181,33 +6211,43 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holmegade 1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t xml:space="preserve">100034625</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F104">
+      <c r="H104">
         <v>2759</v>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t xml:space="preserve">311785873</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-19</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5231,33 +6271,43 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">Holmegade 3</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t xml:space="preserve">100034625</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F105">
+      <c r="H105">
         <v>2095</v>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">311785874</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-19</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5281,33 +6331,43 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5871</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t xml:space="preserve">3013584</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="F106">
+      <c r="H106">
         <v>599</v>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">311789171</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5331,33 +6391,43 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sentvedvej 7</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t xml:space="preserve">3022081</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F107">
+      <c r="H107">
         <v>666</v>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">311789178</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5381,33 +6451,43 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">Provst Hjortsvej 11</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485649</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F108">
+      <c r="H108">
         <v>1034</v>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t xml:space="preserve">311789168</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5431,33 +6511,43 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 140</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t xml:space="preserve">3011021</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F109">
+      <c r="H109">
         <v>713</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t xml:space="preserve">311797133</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5481,33 +6571,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kaliffenlund 3</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t xml:space="preserve">3020021</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="F110">
+      <c r="H110">
         <v>398</v>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t xml:space="preserve">311797117</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5531,33 +6631,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ullerslev-Centret 32</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5540</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
           <t xml:space="preserve">8333766</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F111">
+      <c r="H111">
         <v>1668</v>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t xml:space="preserve">311797113</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5581,33 +6691,43 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kastanievej 1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t xml:space="preserve">9818651</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F112">
+      <c r="H112">
         <v>453</v>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">311797391</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-11-14</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5631,33 +6751,43 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvet 1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484167</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F113">
+      <c r="H113">
         <v>2753</v>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">311829568</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5681,33 +6811,43 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Torvet 1</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484167</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F114">
+      <c r="H114">
         <v>396</v>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t xml:space="preserve">311829568</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5731,33 +6871,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nørrevoldgade 9</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
           <t xml:space="preserve">5484760</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F115">
+      <c r="H115">
         <v>923</v>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t xml:space="preserve">311829489</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5781,33 +6931,43 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Provst Hjortsvej 9D</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t xml:space="preserve">5485614</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="H116">
         <v>630</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">311841344</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-06-27</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5831,33 +6991,43 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017007</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F117">
+      <c r="H117">
         <v>2173</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t xml:space="preserve">311870375</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-26</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5881,33 +7051,43 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 3</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017007</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F118">
+      <c r="H118">
         <v>892</v>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t xml:space="preserve">311870375</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-26</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5931,33 +7111,43 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 3</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
           <t xml:space="preserve">3017007</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="F119">
+      <c r="H119">
         <v>1280</v>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t xml:space="preserve">311870375</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t xml:space="preserve">2035-11-26</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5981,33 +7171,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Odensevej 104B</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5853</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
           <t xml:space="preserve">3014752</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F120">
+      <c r="H120">
         <v>780</v>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="I120" t="inlineStr">
         <is>
           <t xml:space="preserve">311879773</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6031,33 +7231,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ringvej 1C</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
           <t xml:space="preserve">7008389</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F121">
+      <c r="H121">
         <v>1178</v>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="I121" t="inlineStr">
         <is>
           <t xml:space="preserve">311882039</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6081,39 +7291,49 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Svaneparken 4</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5800</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t xml:space="preserve">10226856</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F122">
+      <c r="H122">
         <v>948</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t xml:space="preserve">311882132</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J122"/>
+  <autoFilter ref="A1:L122"/>
 </worksheet>
 </file>
--- a/public/exports/29189722.xlsx
+++ b/public/exports/29189722.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 1</t>
+          <t xml:space="preserve">Alsvej 11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100106793</t>
+          <t xml:space="preserve">3021345</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H2">
-        <v>405</v>
+        <v>774</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 3</t>
+          <t xml:space="preserve">Griffensund 15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100106793</t>
+          <t xml:space="preserve">3016185</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H3">
-        <v>354</v>
+        <v>259</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 102</t>
+          <t xml:space="preserve">Havnegade 30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">101000311</t>
+          <t xml:space="preserve">5483861</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -230,7 +230,7 @@
         </is>
       </c>
       <c r="H4">
-        <v>408</v>
+        <v>625</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 104B</t>
+          <t xml:space="preserve">Havnepromenaden 2A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">101000311</t>
+          <t xml:space="preserve">1337019</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H5">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 104</t>
+          <t xml:space="preserve">Havnepromenaden 6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">101000311</t>
+          <t xml:space="preserve">727892, 1337019</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H6">
-        <v>398</v>
+        <v>560</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepromenaden 2A</t>
+          <t xml:space="preserve">Langtvedvej 11B</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337019</t>
+          <t xml:space="preserve">727965, 3013089</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>369</v>
+        <v>277</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,26 +451,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevangsvej 1A</t>
+          <t xml:space="preserve">Odensevej 98A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">300477, 300478, 300479</t>
+          <t xml:space="preserve">3014776</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H8">
-        <v>2601</v>
+        <v>306</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -526,11 +526,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H9">
-        <v>306</v>
+        <v>792</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odensevej 98A</t>
+          <t xml:space="preserve">Provst Hjortsvej 9E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3014776</t>
+          <t xml:space="preserve">5485614</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H10">
-        <v>792</v>
+        <v>1046</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Griffensund 15</t>
+          <t xml:space="preserve">Ringvej 1B</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016185</t>
+          <t xml:space="preserve">3016999</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H11">
-        <v>259</v>
+        <v>1259</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvej 1B</t>
+          <t xml:space="preserve">Skaboeshusevej 102</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016999</t>
+          <t xml:space="preserve">101000311</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>1259</v>
+        <v>408</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 39A</t>
+          <t xml:space="preserve">Skaboeshusevej 104</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018950</t>
+          <t xml:space="preserve">101000311</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H13">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Skaboeshusevej 104B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018989</t>
+          <t xml:space="preserve">101000311</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H14">
-        <v>420</v>
+        <v>377</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 11</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021345</t>
+          <t xml:space="preserve">3018989</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H15">
-        <v>774</v>
+        <v>420</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,17 +931,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanedamsgade 15</t>
+          <t xml:space="preserve">Skolevænget 1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">305008</t>
+          <t xml:space="preserve">100106793</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="H16">
-        <v>1045</v>
+        <v>405</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wørishøffersgade 25</t>
+          <t xml:space="preserve">Skolevænget 3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">305008, 305009</t>
+          <t xml:space="preserve">100106793</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H17">
-        <v>5698</v>
+        <v>354</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 30</t>
+          <t xml:space="preserve">Stendamsgade 11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5483861</t>
+          <t xml:space="preserve">5484206</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H18">
-        <v>625</v>
+        <v>453</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendamsgade 2</t>
+          <t xml:space="preserve">Stendamsgade 11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484175</t>
+          <t xml:space="preserve">5484206</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H19">
-        <v>333</v>
+        <v>634</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendamsgade 11</t>
+          <t xml:space="preserve">Stendamsgade 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484206</t>
+          <t xml:space="preserve">5484175</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>453</v>
+        <v>333</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendamsgade 11</t>
+          <t xml:space="preserve">Stendamsgade 9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484206</t>
+          <t xml:space="preserve">5484209</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>634</v>
+        <v>939</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stendamsgade 9</t>
+          <t xml:space="preserve">Storebæltsvej 13</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484209</t>
+          <t xml:space="preserve">5486942</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H22">
-        <v>939</v>
+        <v>2858</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Hjortsvej 9E</t>
+          <t xml:space="preserve">Svendborgvej 39A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485614</t>
+          <t xml:space="preserve">3018950</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="H23">
-        <v>1046</v>
+        <v>441</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,40 +1411,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebæltsvej 13</t>
+          <t xml:space="preserve">Solholm 8B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5486942</t>
+          <t xml:space="preserve">3019569</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H24">
-        <v>2858</v>
+        <v>542</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200023926</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepromenaden 6</t>
+          <t xml:space="preserve">Falstervej 15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,30 +1481,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">727892, 1337019</t>
+          <t xml:space="preserve">3021345</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H25">
-        <v>560</v>
+        <v>694</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026224</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langtvedvej 11B</t>
+          <t xml:space="preserve">Skippergade 28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">727965, 3013089</t>
+          <t xml:space="preserve">5484021</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1550,21 +1550,21 @@
         </is>
       </c>
       <c r="H26">
-        <v>277</v>
+        <v>416</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200027009</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-20</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solholm 8B</t>
+          <t xml:space="preserve">Langemosevej 3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3019569</t>
+          <t xml:space="preserve">3021484</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="H27">
-        <v>542</v>
+        <v>264</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023926</t>
+          <t xml:space="preserve">200027854</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falstervej 15</t>
+          <t xml:space="preserve">Skaboeshusevej 98</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,25 +1661,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021345</t>
+          <t xml:space="preserve">5487205</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H28">
-        <v>694</v>
+        <v>1926</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026224</t>
+          <t xml:space="preserve">200028955</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-29</t>
+          <t xml:space="preserve">2020-03-09</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skippergade 28</t>
+          <t xml:space="preserve">Provst Hjortsvej 9A</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484021</t>
+          <t xml:space="preserve">5485651</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="H29">
-        <v>416</v>
+        <v>1320</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027009</t>
+          <t xml:space="preserve">200029367</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-20</t>
+          <t xml:space="preserve">2020-03-17</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langemosevej 3</t>
+          <t xml:space="preserve">Vægtergade 9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021484</t>
+          <t xml:space="preserve">5484150</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="H30">
-        <v>264</v>
+        <v>413</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027854</t>
+          <t xml:space="preserve">200030325</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-10</t>
+          <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 98</t>
+          <t xml:space="preserve">Vægtergade 9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,25 +1841,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487205</t>
+          <t xml:space="preserve">5484150</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H31">
-        <v>1926</v>
+        <v>345</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028955</t>
+          <t xml:space="preserve">200030324</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-09</t>
+          <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Hjortsvej 9A</t>
+          <t xml:space="preserve">Vægtergade 9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,25 +1901,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485651</t>
+          <t xml:space="preserve">5484150</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H32">
-        <v>1320</v>
+        <v>362</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029367</t>
+          <t xml:space="preserve">200030324</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-17</t>
+          <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vægtergade 9</t>
+          <t xml:space="preserve">Egevangsvej 1A</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484150</t>
+          <t xml:space="preserve">300477, 300478, 300479</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="H33">
-        <v>413</v>
+        <v>2601</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030325</t>
+          <t xml:space="preserve">200030440</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-14</t>
+          <t xml:space="preserve">2020-04-16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vægtergade 9</t>
+          <t xml:space="preserve">Alsvej 10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,25 +2021,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484150</t>
+          <t xml:space="preserve">3020770</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H34">
-        <v>345</v>
+        <v>2116</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030324</t>
+          <t xml:space="preserve">200030479</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-14</t>
+          <t xml:space="preserve">2020-04-19</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2071,35 +2071,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vægtergade 9</t>
+          <t xml:space="preserve">Kløvervej 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484150</t>
+          <t xml:space="preserve">8581302</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H35">
-        <v>362</v>
+        <v>1651</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030324</t>
+          <t xml:space="preserve">200030561</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-14</t>
+          <t xml:space="preserve">2020-04-21</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 10</t>
+          <t xml:space="preserve">Havnegade 28</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,25 +2141,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020770</t>
+          <t xml:space="preserve">5483861</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>2116</v>
+        <v>1050</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030479</t>
+          <t xml:space="preserve">200032107</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-19</t>
+          <t xml:space="preserve">2020-06-02</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervej 1</t>
+          <t xml:space="preserve">Hyrdegyden 4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8581302</t>
+          <t xml:space="preserve">5485174</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="H37">
-        <v>1651</v>
+        <v>666</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030561</t>
+          <t xml:space="preserve">200033573</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-21</t>
+          <t xml:space="preserve">2020-07-06</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnegade 28</t>
+          <t xml:space="preserve">Kgs. Bastionsvej 2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,25 +2261,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5483861</t>
+          <t xml:space="preserve">5484337</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032107</t>
+          <t xml:space="preserve">200033798</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-02</t>
+          <t xml:space="preserve">2020-07-09</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2311,17 +2311,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdegyden 4</t>
+          <t xml:space="preserve">Svendborgvej 39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485174</t>
+          <t xml:space="preserve">3018950</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2330,16 +2330,16 @@
         </is>
       </c>
       <c r="H39">
-        <v>666</v>
+        <v>260</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033573</t>
+          <t xml:space="preserve">200034774</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-06</t>
+          <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kgs. Bastionsvej 2</t>
+          <t xml:space="preserve">Dyrehavevej 43</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484337</t>
+          <t xml:space="preserve">3016636</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="H40">
-        <v>1120</v>
+        <v>518</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033798</t>
+          <t xml:space="preserve">200038891</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-09</t>
+          <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 39</t>
+          <t xml:space="preserve">Provst Hjortsvej 9B</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018950</t>
+          <t xml:space="preserve">5485651</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H41">
-        <v>260</v>
+        <v>597</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034774</t>
+          <t xml:space="preserve">200054113</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-02</t>
+          <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrehavevej 43</t>
+          <t xml:space="preserve">Wørishøffersgade 25</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,25 +2501,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016636</t>
+          <t xml:space="preserve">305008, 305009</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H42">
-        <v>518</v>
+        <v>5698</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038891</t>
+          <t xml:space="preserve">311025955</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-11</t>
+          <t xml:space="preserve">2023-11-08</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Hjortsvej 9B</t>
+          <t xml:space="preserve">Nørrevoldgade 63</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,25 +2561,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485651</t>
+          <t xml:space="preserve">5484865</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>597</v>
+        <v>1986</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">200054113</t>
+          <t xml:space="preserve">311070695</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-24</t>
+          <t xml:space="preserve">2024-08-28</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevoldgade 63</t>
+          <t xml:space="preserve">Storebæltsvej 15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,25 +2621,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484865</t>
+          <t xml:space="preserve">5486942</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H44">
-        <v>1986</v>
+        <v>1278</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311070695</t>
+          <t xml:space="preserve">311090709</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-08-28</t>
+          <t xml:space="preserve">2025-01-13</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebæltsvej 15</t>
+          <t xml:space="preserve">Kertemindevej 2A</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5486942</t>
+          <t xml:space="preserve">7074135</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>1278</v>
+        <v>426</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311090709</t>
+          <t xml:space="preserve">311187315</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-13</t>
+          <t xml:space="preserve">2025-11-02</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kertemindevej 2A</t>
+          <t xml:space="preserve">Ringvej 1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7074135</t>
+          <t xml:space="preserve">3016999</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,26 +2750,26 @@
         </is>
       </c>
       <c r="H46">
-        <v>426</v>
+        <v>8061</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311187315</t>
+          <t xml:space="preserve">311395070</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-02</t>
+          <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2806,15 +2806,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H47">
-        <v>8061</v>
+        <v>390</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395070</t>
+          <t xml:space="preserve">311395057</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvej 1</t>
+          <t xml:space="preserve">Ringvej 1D</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2866,15 +2866,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H48">
-        <v>390</v>
+        <v>276</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395057</t>
+          <t xml:space="preserve">311395070</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvej 1D</t>
+          <t xml:space="preserve">Svanedamsgade 2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,20 +2921,20 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016999</t>
+          <t xml:space="preserve">5485003</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>276</v>
+        <v>2193</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395070</t>
+          <t xml:space="preserve">311395074</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2986,11 +2986,11 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H50">
-        <v>2193</v>
+        <v>2889</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3046,11 +3046,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H51">
-        <v>2889</v>
+        <v>734</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3106,11 +3106,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H52">
-        <v>734</v>
+        <v>430</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3166,11 +3166,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H53">
-        <v>430</v>
+        <v>1395</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanedamsgade 2</t>
+          <t xml:space="preserve">Kertemindevej 46</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485003</t>
+          <t xml:space="preserve">3011650</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>1395</v>
+        <v>2675</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311395074</t>
+          <t xml:space="preserve">311407572</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-08-27</t>
+          <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kertemindevej 46</t>
+          <t xml:space="preserve">Skaboeshusevej 100A</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,20 +3341,20 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011650</t>
+          <t xml:space="preserve">5487205</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H56">
-        <v>2675</v>
+        <v>953</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407572</t>
+          <t xml:space="preserve">311407547</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 15</t>
+          <t xml:space="preserve">Skaboeshusevej 100B</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,20 +3401,20 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020547</t>
+          <t xml:space="preserve">5487205</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H57">
-        <v>2042</v>
+        <v>920</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407554</t>
+          <t xml:space="preserve">311407547</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 100B</t>
+          <t xml:space="preserve">Skaboeshusevej 100D</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3466,11 +3466,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H58">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 100D</t>
+          <t xml:space="preserve">Skolevej 15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,20 +3581,20 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487205</t>
+          <t xml:space="preserve">3020547</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>953</v>
+        <v>2042</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407547</t>
+          <t xml:space="preserve">311407554</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 100A</t>
+          <t xml:space="preserve">Skolevej 15C</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,25 +3641,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487205</t>
+          <t xml:space="preserve">3020547</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H61">
-        <v>953</v>
+        <v>437</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407547</t>
+          <t xml:space="preserve">311419854</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-06</t>
+          <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 15C</t>
+          <t xml:space="preserve">Kertemindevej 46</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,25 +3701,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020547</t>
+          <t xml:space="preserve">3011652</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H62">
-        <v>437</v>
+        <v>556</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419854</t>
+          <t xml:space="preserve">311408533</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-11</t>
+          <t xml:space="preserve">2029-11-12</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kertemindevej 46</t>
+          <t xml:space="preserve">Skaboeshusevej 96</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011652</t>
+          <t xml:space="preserve">5487375</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>556</v>
+        <v>1549</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311408533</t>
+          <t xml:space="preserve">311412074</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-12</t>
+          <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3826,15 +3826,15 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>1549</v>
+        <v>749</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412074</t>
+          <t xml:space="preserve">311412071</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skaboeshusevej 96</t>
+          <t xml:space="preserve">Pårupvej 25B</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487375</t>
+          <t xml:space="preserve">3017687</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>749</v>
+        <v>513</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412071</t>
+          <t xml:space="preserve">311414590</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-03</t>
+          <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3946,11 +3946,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4006,11 +4006,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H67">
-        <v>487</v>
+        <v>459</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4066,11 +4066,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H68">
-        <v>459</v>
+        <v>613</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4126,11 +4126,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H69">
-        <v>613</v>
+        <v>407</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,35 +4171,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pårupvej 25B</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5871</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3017687</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>407</v>
+        <v>986</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414590</t>
+          <t xml:space="preserve">311428334</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-18</t>
+          <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4246,11 +4246,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H71">
-        <v>986</v>
+        <v>1281</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4306,15 +4306,15 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H72">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428341</t>
+          <t xml:space="preserve">311428343</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Skolevej 1A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4366,15 +4366,15 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H73">
-        <v>1281</v>
+        <v>314</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428334</t>
+          <t xml:space="preserve">311428341</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Langemosevej 1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5871</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">3021483</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H74">
-        <v>254</v>
+        <v>2410</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428343</t>
+          <t xml:space="preserve">311429648</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-17</t>
+          <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H75">
-        <v>2410</v>
+        <v>556</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langemosevej 1</t>
+          <t xml:space="preserve">Sentvedvej 4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4726,20 +4726,20 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H79">
-        <v>556</v>
+        <v>332</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311429648</t>
+          <t xml:space="preserve">311432562</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-24</t>
+          <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sentvedvej 4</t>
+          <t xml:space="preserve">Ravnekærlund 1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021483</t>
+          <t xml:space="preserve">100007616</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>332</v>
+        <v>1000</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311432562</t>
+          <t xml:space="preserve">311459391</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-14</t>
+          <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnekærlund 1</t>
+          <t xml:space="preserve">Tårnvej 13</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100007616</t>
+          <t xml:space="preserve">5485861</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,11 +4850,11 @@
         </is>
       </c>
       <c r="H81">
-        <v>1000</v>
+        <v>1206</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459391</t>
+          <t xml:space="preserve">311459380</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tårnvej 13</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485861</t>
+          <t xml:space="preserve">3018989</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>1206</v>
+        <v>5915</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459380</t>
+          <t xml:space="preserve">311479309</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-07</t>
+          <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 1</t>
+          <t xml:space="preserve">Sylleskovvej 10</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">10109499</t>
+          <t xml:space="preserve">8053584</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,11 +4970,11 @@
         </is>
       </c>
       <c r="H83">
-        <v>826</v>
+        <v>1157</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479299</t>
+          <t xml:space="preserve">311479296</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5011,17 +5011,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Ådalen 1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018989</t>
+          <t xml:space="preserve">10109499</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,11 +5030,11 @@
         </is>
       </c>
       <c r="H84">
-        <v>5915</v>
+        <v>826</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479309</t>
+          <t xml:space="preserve">311479299</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sylleskovvej 10</t>
+          <t xml:space="preserve">Harevænget 30</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8053584</t>
+          <t xml:space="preserve">5487254</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>1157</v>
+        <v>594</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311479296</t>
+          <t xml:space="preserve">311493575</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-30</t>
+          <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,35 +5131,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harevænget 30</t>
+          <t xml:space="preserve">Odensevej 100</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5487254</t>
+          <t xml:space="preserve">727972, 3014752</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H86">
-        <v>594</v>
+        <v>670</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311493575</t>
+          <t xml:space="preserve">311572425</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-08</t>
+          <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5251,30 +5251,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 7A</t>
+          <t xml:space="preserve">Skolevænget 4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484485</t>
+          <t xml:space="preserve">9594304</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H88">
-        <v>424</v>
+        <v>2841</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572484</t>
+          <t xml:space="preserve">311572368</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5311,30 +5311,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odensevej 100</t>
+          <t xml:space="preserve">Vestergade 7A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">727972, 3014752</t>
+          <t xml:space="preserve">5484485</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>670</v>
+        <v>424</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572425</t>
+          <t xml:space="preserve">311572484</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 4</t>
+          <t xml:space="preserve">Sportsvænget 4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5871</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9594304</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H90">
-        <v>2841</v>
+        <v>690</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572368</t>
+          <t xml:space="preserve">311575186</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-14</t>
+          <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvænget 4</t>
+          <t xml:space="preserve">Sportsvænget 4A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,20 +5441,20 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">3013584, 100480677</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H91">
-        <v>690</v>
+        <v>549</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575186</t>
+          <t xml:space="preserve">311575158</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5491,35 +5491,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvænget 4A</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5871</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584, 100480677</t>
+          <t xml:space="preserve">3018989</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H92">
-        <v>549</v>
+        <v>5226</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575158</t>
+          <t xml:space="preserve">311576469</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-27</t>
+          <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,30 +5551,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Storebæltsvej 15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018989</t>
+          <t xml:space="preserve">5486942</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>5226</v>
+        <v>1278</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576469</t>
+          <t xml:space="preserve">311576597</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5626,15 +5626,15 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H94">
-        <v>1278</v>
+        <v>1470</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576597</t>
+          <t xml:space="preserve">311576575</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5686,11 +5686,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H95">
-        <v>1470</v>
+        <v>2096</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5731,35 +5731,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storebæltsvej 15</t>
+          <t xml:space="preserve">Bytoften 25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5486942</t>
+          <t xml:space="preserve">3017767</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>2096</v>
+        <v>282</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576575</t>
+          <t xml:space="preserve">311586393</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-03</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 25</t>
+          <t xml:space="preserve">Skolevej 15B</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3017767</t>
+          <t xml:space="preserve">727934, 3020550</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>282</v>
+        <v>1300</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586393</t>
+          <t xml:space="preserve">311603945</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-05-30</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 15B</t>
+          <t xml:space="preserve">Langemosevej 5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">727934, 3020550</t>
+          <t xml:space="preserve">3021483</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H98">
-        <v>1300</v>
+        <v>2506</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311603945</t>
+          <t xml:space="preserve">311620632</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-30</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5926,11 +5926,11 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H99">
-        <v>2506</v>
+        <v>1548</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5986,15 +5986,15 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H100">
-        <v>1548</v>
+        <v>1076</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620632</t>
+          <t xml:space="preserve">311620639</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langemosevej 5</t>
+          <t xml:space="preserve">Halvej 1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3021483</t>
+          <t xml:space="preserve">5485155</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H101">
-        <v>1076</v>
+        <v>4111</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620639</t>
+          <t xml:space="preserve">311643736</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halvej 1</t>
+          <t xml:space="preserve">Kertemindevej 50</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,25 +6101,25 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485155</t>
+          <t xml:space="preserve">3011660</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H102">
-        <v>4111</v>
+        <v>1635</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643736</t>
+          <t xml:space="preserve">311644019</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-21</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kertemindevej 50</t>
+          <t xml:space="preserve">Holmegade 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,25 +6161,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3011660</t>
+          <t xml:space="preserve">100034625</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H103">
-        <v>1635</v>
+        <v>2759</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644024</t>
+          <t xml:space="preserve">311785873</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2034-09-19</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegade 1</t>
+          <t xml:space="preserve">Holmegade 3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6226,15 +6226,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>2759</v>
+        <v>2095</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311785873</t>
+          <t xml:space="preserve">311785874</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegade 3</t>
+          <t xml:space="preserve">Provst Hjortsvej 11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100034625</t>
+          <t xml:space="preserve">5485649</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H105">
-        <v>2095</v>
+        <v>1034</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311785874</t>
+          <t xml:space="preserve">311789168</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-19</t>
+          <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,30 +6331,30 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Sentvedvej 7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5871</t>
+          <t xml:space="preserve">5853</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3013584</t>
+          <t xml:space="preserve">3022081</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>599</v>
+        <v>666</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789171</t>
+          <t xml:space="preserve">311789178</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6391,30 +6391,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sentvedvej 7</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5853</t>
+          <t xml:space="preserve">5871</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3022081</t>
+          <t xml:space="preserve">3013584</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H107">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789178</t>
+          <t xml:space="preserve">311789171</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6451,35 +6451,35 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Hjortsvej 11</t>
+          <t xml:space="preserve">Kaliffenlund 3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800</t>
+          <t xml:space="preserve">5540</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485649</t>
+          <t xml:space="preserve">3020021</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H108">
-        <v>1034</v>
+        <v>398</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311789168</t>
+          <t xml:space="preserve">311797117</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-03</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaliffenlund 3</t>
+          <t xml:space="preserve">Ullerslev-Centret 32</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,20 +6581,20 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020021</t>
+          <t xml:space="preserve">8333766</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H110">
-        <v>398</v>
+        <v>1668</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797117</t>
+          <t xml:space="preserve">311797113</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ullerslev-Centret 32</t>
+          <t xml:space="preserve">Kastanievej 1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">5800</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8333766</t>
+          <t xml:space="preserve">9818651</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,16 +6650,16 @@
         </is>
       </c>
       <c r="H111">
-        <v>1668</v>
+        <v>453</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797113</t>
+          <t xml:space="preserve">311797391</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2034-11-14</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 1</t>
+          <t xml:space="preserve">Nørrevoldgade 9</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,25 +6701,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9818651</t>
+          <t xml:space="preserve">5484760</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H112">
-        <v>453</v>
+        <v>923</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797391</t>
+          <t xml:space="preserve">311829489</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-14</t>
+          <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevoldgade 9</t>
+          <t xml:space="preserve">Provst Hjortsvej 9D</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5484760</t>
+          <t xml:space="preserve">5485614</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H115">
-        <v>923</v>
+        <v>630</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829489</t>
+          <t xml:space="preserve">311841344</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-06</t>
+          <t xml:space="preserve">2035-06-27</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provst Hjortsvej 9D</t>
+          <t xml:space="preserve">Svanedamsgade 15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5485614</t>
+          <t xml:space="preserve">305008</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>630</v>
+        <v>1045</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311841344</t>
+          <t xml:space="preserve">311842900</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-27</t>
+          <t xml:space="preserve">2035-07-04</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">

--- a/public/exports/29189722.xlsx
+++ b/public/exports/29189722.xlsx
@@ -5154,7 +5154,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572425</t>
+          <t xml:space="preserve">311572431</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572425</t>
+          <t xml:space="preserve">311572431</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">

--- a/public/exports/29189722.xlsx
+++ b/public/exports/29189722.xlsx
@@ -6114,7 +6114,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644019</t>
+          <t xml:space="preserve">311644024</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">

--- a/public/exports/29189722.xlsx
+++ b/public/exports/29189722.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:M122"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Svendborg)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Svendborg)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-29</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-20</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-10</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-09</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-17</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-14</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1979,15 +2139,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-16</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-19</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-04-21</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-02</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-06</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-09</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-02</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2399,15 +2594,20 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-11</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Svendborg)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-24</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-11-08</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-08-28</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-01-13</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-11-02</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-08-27</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-06</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-11</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-11-12</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-03</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-12-18</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4314,20 +4669,25 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311428343</t>
+          <t xml:space="preserve">311428341</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-24</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-04-14</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-07</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-30</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-02-08</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5154,20 +5579,25 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572431</t>
+          <t xml:space="preserve">311572425</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5214,20 +5644,25 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572431</t>
+          <t xml:space="preserve">311572425</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-14</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-27</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-02-03</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-05-30</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-21</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6114,20 +6619,25 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644024</t>
+          <t xml:space="preserve">311644019</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Andel Energi A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-19</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-19</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-03</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-14</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-27</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-04</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-26</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-26</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-26</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-02</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,21 +7924,26 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L122"/>
+  <autoFilter ref="A1:M122"/>
 </worksheet>
 </file>